--- a/SS_lcbw_input.xlsx
+++ b/SS_lcbw_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\Task_FY25_NCMP_Part_1\Chicago_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_StormSim_Task\StormSim-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBA88D1-4AA1-4A9C-9437-BEA9F0A6DD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7E8E65-87D5-4056-8F77-64403EE2AE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="28800" windowHeight="15345" xr2:uid="{DCE98FF7-F0BD-48B7-BD15-98C25A65ECBE}"/>
+    <workbookView xWindow="-38520" yWindow="990" windowWidth="38640" windowHeight="21120" xr2:uid="{DCE98FF7-F0BD-48B7-BD15-98C25A65ECBE}"/>
   </bookViews>
   <sheets>
     <sheet name="lowcrestedBW" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="172">
   <si>
     <t>StormSim Project General Inputs</t>
   </si>
@@ -546,6 +546,12 @@
   </si>
   <si>
     <t>Roughness Coefficient, 2 for grass; 1 for concrete, asphalt, or closed blocks; 0.9 for basalt or placed revetment blocks; 0.8 for stepped structure; Table 6.2 from EurOtop (2018) (rubble mound )</t>
+  </si>
+  <si>
+    <t>compute_wave_transmission</t>
+  </si>
+  <si>
+    <t>Compute wave transmission (eurotop)</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1317,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A47BBA17-74C1-4E3D-B059-DCBBE7E0FD59}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="101.7109375" customWidth="1"/>
@@ -2412,10 +2418,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>109</v>
+        <v>171</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>10</v>
@@ -2426,51 +2432,65 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D60" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B62" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="C61" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D61" s="2">
+      <c r="C62" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="46"/>
-      <c r="B62" s="46"/>
-      <c r="C62" s="46"/>
-      <c r="D62" s="46"/>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="46"/>
+      <c r="B63" s="46"/>
+      <c r="C63" s="46"/>
+      <c r="D63" s="46"/>
     </row>
   </sheetData>
   <sheetProtection formatColumns="0" selectLockedCells="1"/>
